--- a/data/trans_orig/IP3109_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Clase-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>45279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61467</t>
+          <t>62970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77872</t>
+          <t>77726</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>109624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157861</t>
+          <t>157058</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183524</t>
+          <t>182156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44922</t>
+          <t>45027</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55146</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>69926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50612</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>65857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110138</t>
+          <t>109424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131763</t>
+          <t>131592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45447</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61558</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80641</t>
+          <t>80191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>31928</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>42505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>70969</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>120675</t>
+          <t>119053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129810</t>
+          <t>131430</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>170568</t>
+          <t>172410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114421</t>
+          <t>114539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>145582</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>253745</t>
+          <t>254381</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>307189</t>
+          <t>307625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>34141</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>38566</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63274</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>81602</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>92033</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>117532</t>
+          <t>118319</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>160146</t>
+          <t>161916</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>191384</t>
+          <t>192403</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>789</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>56182</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>49720</t>
+          <t>49569</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81832</t>
+          <t>84246</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>101256</t>
+          <t>102480</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>73978</t>
+          <t>74121</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>70267</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>100912</t>
+          <t>99654</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>123320</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>165241</t>
+          <t>164783</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>98420</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>140928</t>
+          <t>139887</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>126114</t>
+          <t>126018</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>168851</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>233616</t>
+          <t>234501</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>293784</t>
+          <t>297735</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>413761</t>
+          <t>410950</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>464562</t>
+          <t>463840</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>451422</t>
+          <t>448381</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>500385</t>
+          <t>501228</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>876223</t>
+          <t>873406</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>949547</t>
+          <t>953075</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6573</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7412</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9426</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12338</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13305</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7995</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19742</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20730</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13956</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12128</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18346</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>34274</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>24738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45279</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>79126</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97229</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>65,28%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>70235</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>62970</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>77726</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>69,05%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100608</t>
+          <t>68262</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90693</t>
+          <t>60174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109624</t>
+          <t>75852</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170843</t>
+          <t>157296</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157058</t>
+          <t>144760</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182156</t>
+          <t>168150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5870</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5270</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1880</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8497</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3108</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7715</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8554</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4538</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18153</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12238</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24782</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17583</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>11943</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>23822</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45027</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56738</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49312</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>64497</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>62620</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>55293</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>69926</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>67,05%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>64153</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50313</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65857</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121286</t>
+          <t>120891</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109424</t>
+          <t>109289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>131626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10023</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6006</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>15701</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>17,95%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>28,12%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>8472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7413</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3849</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11714</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11121</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6270</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17923</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>35,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>36268</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>29781</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>41567</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>64,94%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>74,43%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>26762</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>38280</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>65,65%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45411</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>71730</t>
+          <t>70304</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>61206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80191</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>357</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,92 +3233,92 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3769</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10224</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>6701</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>11833</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12363</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26696</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8671</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>23962</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>37199</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>44830</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>52157</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>39518</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>66383</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>26,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>33,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>42026</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>26190</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>57513</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42505</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70969</t>
+          <t>45265</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>97334</t>
+          <t>87830</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75462</t>
+          <t>73715</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>119053</t>
+          <t>105877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>121071</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>107080</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>135661</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>61,36%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>54,27%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>68,75%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>147284</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>131430</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>172410</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>61,21%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>80,3%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>130232</t>
+          <t>114928</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114539</t>
+          <t>104969</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>125520</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>277516</t>
+          <t>235998</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>254381</t>
+          <t>215941</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>307625</t>
+          <t>251021</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>543</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,92 +3915,92 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>5106</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>8776</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>5467</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4013,107 +4013,107 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>4038</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>5362</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>8168</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2148</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5799</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>20846</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>13880</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>29382</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>14,37%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20,25%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>13873</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>9008</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>20283</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29044</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49563</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>16627</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>33229</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>25874</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>19175</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>35315</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>50734</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>94105</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>83313</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>106034</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>64,87%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>57,43%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>72961</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>64784</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>81683</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>70,72%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>103783</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>62219</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>176744</t>
+          <t>165515</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>161916</t>
+          <t>151724</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>181137</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>145074</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>145074</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>145074</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>115466</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>115466</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>115466</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>158896</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>158896</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>158896</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>274405</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>274405</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>274405</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2257</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>5828</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>5359</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>9517</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5147,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>16958</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>23441</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>10381</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>16407</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>40569</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>33758</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>47150</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>61,6%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>71,59%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>50645</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>43920</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>56183</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>73,51%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>63,75%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>81,55%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>51673</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>49569</t>
+          <t>56997</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>93087</t>
+          <t>92242</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>84246</t>
+          <t>82580</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>102480</t>
+          <t>101370</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,42%</t>
         </is>
       </c>
     </row>
@@ -5373,74 +5373,74 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>183</t>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>5825</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>19296</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>28400</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>21091</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>14229</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>30222</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,22 +5791,22 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>33057</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>54197</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>71871</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>58194</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>85332</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>60512</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>48095</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>74121</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>83964</t>
+          <t>60802</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>73642</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>144476</t>
+          <t>132673</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>123320</t>
+          <t>114943</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>164783</t>
+          <t>150996</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>139410</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>120222</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>159691</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>17,81%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>119114</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>99631</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>139887</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>145576</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>126018</t>
+          <t>100018</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>132331</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>264689</t>
+          <t>255386</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>234501</t>
+          <t>229135</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>297735</t>
+          <t>281102</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>437784</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>412292</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>460238</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>64,84%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>61,06%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>68,16%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>590</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>436630</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>410950</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>463840</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>67,77%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>71,99%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>474575</t>
+          <t>404462</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>448381</t>
+          <t>382981</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>501228</t>
+          <t>423252</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>911206</t>
+          <t>842246</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>873406</t>
+          <t>811728</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>953075</t>
+          <t>875728</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -6168,74 +6168,74 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>675183</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>675183</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>675183</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>901</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>644306</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>644306</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>644306</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>609358</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>609358</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>609358</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>731803</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>731803</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>731803</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>1823</t>
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1376110</t>
+          <t>1284541</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1376110</t>
+          <t>1284541</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1376110</t>
+          <t>1284541</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
